--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07300000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.024</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>0.027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.045</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.042</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.034</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.007</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.027</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002000000000000002</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.012</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.007</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.003000000000000003</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.014</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.077</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.033</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.044</v>
+        <v>0.007</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.021</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.055</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>0.058</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.197</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.068</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.129</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.143</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.043</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.054</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.026</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.128</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>0.016</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.112</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.227</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.202</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.392</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.36</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.401</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.043</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.107</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>0.044</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.063</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.011</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.066</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.057</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,27 +1281,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>region_Middle_East_and_Africa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>region_North_America</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C33" t="n">
         <v>0.022</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.007999999999999998</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
+      <c r="D33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1361,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9952614504155347</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1298633463115101</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.630560047471351</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.129699880048327</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630026169528008</v>
+        <v>1.67804342107184</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.795305922714377</v>
+        <v>1.749032162934507</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09889889450250967</v>
+        <v>0.0997233061900074</v>
       </c>
       <c r="D2" t="n">
-        <v>1.601467651378632</v>
+        <v>1.553578074382832</v>
       </c>
       <c r="E2" t="n">
-        <v>1.989144194050123</v>
+        <v>1.944486251486182</v>
       </c>
       <c r="F2" t="n">
-        <v>1.217037052960616e-73</v>
+        <v>7.237657289196959e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1462,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02940556654077835</v>
+        <v>0.02962572488141942</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01869201971224752</v>
+        <v>0.01822264113750337</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.007230118893539535</v>
+        <v>-0.006089995451285204</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06604125197509622</v>
+        <v>0.06534144521412404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1156814179394445</v>
+        <v>0.1039997416774884</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1487,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09627845604584455</v>
+        <v>0.09776307597911857</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05077087895837804</v>
+        <v>0.04954667549874947</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.003230638176018874</v>
+        <v>0.0006533764478764831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.195787550267708</v>
+        <v>0.1948727755103606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05791612198436446</v>
+        <v>0.04847835276759659</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1512,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01190082236172661</v>
+        <v>-0.0128759363155794</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03166308253320829</v>
+        <v>0.03341847660338247</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07395932376633413</v>
+        <v>-0.07837494687640348</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0501576790428809</v>
+        <v>0.05262307424524468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7070224780821377</v>
+        <v>0.7000196553266504</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1537,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04925140976485315</v>
+        <v>0.04934458162077567</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03212440036822781</v>
+        <v>0.03238690772777993</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0137112579818186</v>
+        <v>-0.01413259109629494</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1122140775115249</v>
+        <v>0.1128217543378463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1252397797480165</v>
+        <v>0.1276095198106732</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1562,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01087375428095371</v>
+        <v>0.01045597826565331</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03159620614141574</v>
+        <v>0.03252310347467072</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05105367180432441</v>
+        <v>-0.05328813321017078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07280118036623184</v>
+        <v>0.0742000897414774</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7307353878115517</v>
+        <v>0.7478361600842374</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1587,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06490436425824865</v>
+        <v>0.06434814183682909</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03167065878647472</v>
+        <v>0.03290386814872377</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00283101367010119</v>
+        <v>-0.0001422546867241303</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1269777148463961</v>
+        <v>0.1288385383603823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04042759518403131</v>
+        <v>0.05050750165873737</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1612,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02833304077029527</v>
+        <v>0.02877420831517304</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03146560475697377</v>
+        <v>0.03191215009447936</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03333841130514552</v>
+        <v>-0.03377245653924299</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09000449284573606</v>
+        <v>0.09132087316958906</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3678835786953364</v>
+        <v>0.3672325279422073</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1637,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0007305232281143312</v>
+        <v>-0.00101898420932277</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05004783037595575</v>
+        <v>0.05063846000222128</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09736142181312865</v>
+        <v>-0.1002685420462485</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09882246826935731</v>
+        <v>0.09823057362760301</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9883540904034334</v>
+        <v>0.9839454655173241</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1662,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01947630172576837</v>
+        <v>0.01931633161945881</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05056707783221254</v>
+        <v>0.05194329107217195</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07963334962880197</v>
+        <v>-0.08249064812047914</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1185859530803387</v>
+        <v>0.1211233113593968</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7001205466429863</v>
+        <v>0.7099870626555924</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1687,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06975733017854038</v>
+        <v>0.0677289801249665</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05280002815808037</v>
+        <v>0.05163557818882266</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03372882339399788</v>
+        <v>-0.03347489344602786</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1732434837510786</v>
+        <v>0.1689328536959609</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1864477365257986</v>
+        <v>0.1896305795997606</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1712,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04002893971901898</v>
+        <v>0.03988129614662063</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05135700222668233</v>
+        <v>0.05171813694708186</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06062893499922174</v>
+        <v>-0.06148438961717011</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1406868144372597</v>
+        <v>0.1412469819104114</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4357293071518438</v>
+        <v>0.4406311499162626</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1737,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01308395424465889</v>
+        <v>0.01333034569364371</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05142429100061102</v>
+        <v>0.05322085593893354</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08770580404704592</v>
+        <v>-0.09098061517306066</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1138737125363637</v>
+        <v>0.1176413065603481</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7991622968663248</v>
+        <v>0.802222188907029</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1762,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05355806804976877</v>
+        <v>0.05372608150388216</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05063980406704115</v>
+        <v>0.05226717408728829</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04569412410579684</v>
+        <v>-0.04871569728088807</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1528102602053344</v>
+        <v>0.1561678602886524</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2902251318665611</v>
+        <v>0.3039909897906226</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1787,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04060048178851764</v>
+        <v>0.04075528353732605</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05103518098339139</v>
+        <v>0.05309570953627988</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.05942663488341294</v>
+        <v>-0.06331039488738241</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1406275984604482</v>
+        <v>0.1448209619620345</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4262999777771964</v>
+        <v>0.4427358660730101</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1812,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01196129292955408</v>
+        <v>0.01088254976687354</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05001536298694156</v>
+        <v>0.05158432471739408</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08606701719854903</v>
+        <v>-0.09022086884603817</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1099896030576572</v>
+        <v>0.1119859683797853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8109874291209526</v>
+        <v>0.8329136341204477</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1837,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02852949115213387</v>
+        <v>0.0286319469098267</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04938241430174458</v>
+        <v>0.04992876705012336</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0682582623489212</v>
+        <v>-0.06922663830090525</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1253172446531889</v>
+        <v>0.1264905321205586</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5634493076266474</v>
+        <v>0.5663360387177493</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1862,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009855163262129219</v>
+        <v>0.009518215481816597</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05042031777262197</v>
+        <v>0.05189167694291168</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08896684366127464</v>
+        <v>-0.09218760242367784</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1086771701855331</v>
+        <v>0.111224033387311</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8450327256382217</v>
+        <v>0.854464793714935</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1887,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01283656674590102</v>
+        <v>-0.01322088667279</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05046836942870858</v>
+        <v>0.04979291726953827</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1117527531846321</v>
+        <v>-0.1108132112062675</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08607961969283011</v>
+        <v>0.0843714378606875</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7992261397199898</v>
+        <v>0.7906108960257916</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1912,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003964408262729715</v>
+        <v>0.004335437062310128</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04992011791449898</v>
+        <v>0.05125049584123835</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09387722495368103</v>
+        <v>-0.09611368897633686</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1018060414791405</v>
+        <v>0.1047845631009571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9367025046124571</v>
+        <v>0.9325849043145348</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1937,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0115274840431817</v>
+        <v>0.01158397950368169</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05322180864532769</v>
+        <v>0.05351623953049025</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09278534409374306</v>
+        <v>-0.09330592256409793</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1158403121801065</v>
+        <v>0.1164738815714613</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8285253533638773</v>
+        <v>0.8286313234472755</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1962,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04496309656699375</v>
+        <v>0.04490126550683204</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05113184316026088</v>
+        <v>0.05073590126058453</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05525347449026828</v>
+        <v>-0.05453927368709396</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1451796676242558</v>
+        <v>0.144341804700758</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3792082441723256</v>
+        <v>0.3761567069305498</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -1987,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09307215757813245</v>
+        <v>0.09277287691209153</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04186214334283192</v>
+        <v>0.04198074945144141</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01102386431052869</v>
+        <v>0.01049211994326674</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1751204508457362</v>
+        <v>0.1750536338809163</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02619549014576178</v>
+        <v>0.02711273375311711</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2012,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03608399240237126</v>
+        <v>0.0360786356075037</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02420456206757936</v>
+        <v>0.02485846017140067</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01135607751164863</v>
+        <v>-0.01264305103956499</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08352406231639115</v>
+        <v>0.0848003222545724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1360158425228071</v>
+        <v>0.1466789605900473</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2037,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0141164021840652</v>
+        <v>0.01448398768324711</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02904880359700642</v>
+        <v>0.02811551845289983</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04281820666004497</v>
+        <v>-0.04062141589110786</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07105101102817536</v>
+        <v>0.06958939125760208</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6269992953929717</v>
+        <v>0.6064412877410574</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2062,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03294031018818389</v>
+        <v>-0.03309843316687123</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02954020551570261</v>
+        <v>0.02920935542237533</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09083804909487245</v>
+        <v>-0.09034771780635661</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02495742871850468</v>
+        <v>0.02415085147261416</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2648071796263858</v>
+        <v>0.2571533936244728</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2087,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01346309111604451</v>
+        <v>-0.01378326527887544</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02938900456741658</v>
+        <v>0.02964373700932217</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07106448160966417</v>
+        <v>-0.07188392218432399</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04413829937757514</v>
+        <v>0.0443173916265731</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6468808892453798</v>
+        <v>0.6419573641976883</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2112,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02668680021059644</v>
+        <v>-0.02693520877969164</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02900282836882117</v>
+        <v>0.02936902969487703</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08353129926328248</v>
+        <v>-0.08449744924253799</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03015769884208961</v>
+        <v>0.03062703168315472</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3574971227482281</v>
+        <v>0.3590746904262956</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2137,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4005965890818798</v>
+        <v>0.3982233096578141</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03981363902264499</v>
+        <v>0.03926983810596111</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3225632905040172</v>
+        <v>0.3212558412914117</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4786298876597425</v>
+        <v>0.4751907780242164</v>
       </c>
       <c r="F30" t="n">
-        <v>8.150040732680005e-24</v>
+        <v>3.645104327879786e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2158,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.006477868982296107</v>
+        <v>-0.002085975822998771</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003987866461712084</v>
+        <v>0.001402357375237836</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01429394362240697</v>
+        <v>-0.004834545771919052</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001338205657814756</v>
+        <v>0.0006625941259215105</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1042916061882443</v>
+        <v>0.1368885945885609</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2183,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4979186601504517</v>
+        <v>-0.001517501047856209</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01239166192331236</v>
+        <v>0.00159977479550116</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4736314490721631</v>
+        <v>-0.004653002030413412</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5222058712287402</v>
+        <v>0.001617999934700994</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.3428385058225838</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2208,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001526159158865509</v>
+        <v>0.4975842499220143</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001623369780325839</v>
+        <v>0.01226979046800349</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004707905461894853</v>
+        <v>0.4735359025068746</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001655587144163835</v>
+        <v>0.5216325973371539</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3471570343679481</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2233,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.002067808365076527</v>
+        <v>-0.003190404661875361</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001370665326112665</v>
+        <v>0.004191906749099856</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004754263039115197</v>
+        <v>-0.01140639091666146</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0006186463089621441</v>
+        <v>0.005025581592910739</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1313968079804144</v>
+        <v>0.4466052571656757</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2262,21 +2289,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.639582597638929</v>
+        <v>1.638035829451045</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04788415812916749</v>
+        <v>0.04812529240022996</v>
       </c>
       <c r="D35" t="n">
-        <v>1.54573137227574</v>
+        <v>1.543711989601135</v>
       </c>
       <c r="E35" t="n">
-        <v>1.733433823002118</v>
+        <v>1.732359669300955</v>
       </c>
       <c r="F35" t="n">
-        <v>6.018033914196592e-257</v>
+        <v>6.341968535623971e-254</v>
       </c>
       <c r="G35" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.001072258730903541</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001289206013563249</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.001454538624332883</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.003599056086139966</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4055668752339265</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2291,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.424595366175215</v>
+        <v>-2.680600179802938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4699812973694731</v>
+        <v>0.4771933030981325</v>
       </c>
       <c r="D2" t="n">
-        <v>2.483799515165129e-07</v>
+        <v>1.938181768271168e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2339,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327040559</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767081015513708</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260429188259</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627192</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794775545217</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990748904945</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2371,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127299</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1689953683152051</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561359606461e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749496686</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765738941879</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175529024153</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2403,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.275906022416754</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662634417183</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831375553563</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505724593</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040242209362</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.576571189971413</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2435,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.871778570870576</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649218702299</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065613561488396e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2451,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.037352240367789</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916813503851</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265467947022</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2467,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2713985237416621</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070653033665</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717882228968</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2483,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319905862</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.258092362680186</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974971355069</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2499,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04068301518422479</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004784975071</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799211234182</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2515,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05345693884495933</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638610262009</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532575785491</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2531,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042277773</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.25992806241409</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6335050825508384</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2547,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312141687</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901907586843</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9942297799667277</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2563,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378426662</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2586555011338381</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132626676296</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2579,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712348868</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604874679544</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023734866079</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2595,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928780688</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260713514327</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9312248636975232</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2611,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434463961</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.265659520794061</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682492664</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2627,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2096018965396373</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2485899459155399</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371714945826</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2643,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509214496</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515009079846</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543635085022</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2659,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641810814</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423511374601</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08910387128184533</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
@@ -2675,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.939948370751521</v>
+        <v>0.9366864721074267</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1570978378415049</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.187908098302239e-09</v>
+        <v>2.713396260923891e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2691,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5774584503453005</v>
+        <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1153148485868671</v>
+        <v>0.1143619392421807</v>
       </c>
       <c r="D25" t="n">
-        <v>5.50935246170832e-07</v>
+        <v>4.401383208103943e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2707,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2375989005820144</v>
+        <v>0.237316144844174</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1483942012834082</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1093473930483596</v>
+        <v>0.1145360411757813</v>
       </c>
     </row>
     <row r="27">
@@ -2723,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04390400011939626</v>
+        <v>-0.04350476117998651</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1581709974635947</v>
+        <v>0.1611879340386412</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7813401518906566</v>
+        <v>0.7872365295400213</v>
       </c>
     </row>
     <row r="28">
@@ -2739,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07706864556787009</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1578050341313147</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6252814998540484</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
@@ -2755,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09735884295377209</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1528329758433737</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5241067842939673</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0214099884697233</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02125751820946937</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3138518697701007</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
@@ -2787,29 +2839,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004963851467081969</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008295015527615652</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5495638837811058</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002369150025834419</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007250684388774151</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7438581373219401</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
@@ -2819,13 +2871,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.228992117455078</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1106079911201261</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03842392670187963</v>
+        <v>0.04668969945129923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.006335499136474495</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.006871422968197181</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
